--- a/tests/Crystal_test.xlsx
+++ b/tests/Crystal_test.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277B4A0E-0531-1441-80BB-9C719F9505EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6FCA76-62E1-6A4D-B800-534DC25B2088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7700" yWindow="500" windowWidth="28140" windowHeight="21900" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
   <si>
     <t>REACTION</t>
   </si>
@@ -168,6 +168,39 @@
   </si>
   <si>
     <t>Orthrombic</t>
+  </si>
+  <si>
+    <t>Number of Balls</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>in text, they say this was done in a tungsten carbide cell, in table it is specified as stainless steel</t>
+  </si>
+  <si>
+    <t>WORKUPS</t>
+  </si>
+  <si>
+    <t>Filtration</t>
+  </si>
+  <si>
+    <t>OBSERVATIONS</t>
+  </si>
+  <si>
+    <t>murky</t>
+  </si>
+  <si>
+    <t>ethyl acetate</t>
+  </si>
+  <si>
+    <t>Amount (unmeasured)</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -203,12 +236,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -224,11 +263,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -564,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C7A012-DC9A-214C-8A2F-E48641012DAD}">
-  <dimension ref="A3:P54"/>
+  <dimension ref="A3:V54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -579,8 +619,8 @@
     <col min="11" max="11" width="10.83203125" style="1"/>
     <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" style="1"/>
-    <col min="14" max="14" width="16.6640625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="1"/>
+    <col min="14" max="15" width="16.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -608,8 +648,8 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K12" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>0</v>
       </c>
     </row>
@@ -650,7 +690,7 @@
       </c>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -677,12 +717,12 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>5</v>
       </c>
@@ -701,13 +741,19 @@
       <c r="N19" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="S19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -753,13 +799,31 @@
       <c r="P21" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="Q21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
@@ -793,8 +857,20 @@
       <c r="N23" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="S23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>38</v>
       </c>
@@ -829,7 +905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
@@ -863,8 +939,11 @@
       <c r="N25" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
@@ -899,22 +978,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="11:12" x14ac:dyDescent="0.2">
